--- a/artfynd/A 22179-2022 artfynd.xlsx
+++ b/artfynd/A 22179-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22179-2022 artfynd.xlsx
+++ b/artfynd/A 22179-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79774877</v>
+        <v>79774897</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607315.4208568152</v>
+        <v>607626</v>
       </c>
       <c r="R2" t="n">
-        <v>7218046.122854709</v>
+        <v>7218010</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2019-09-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79774864</v>
+        <v>94318512</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grönberget, Ly lm</t>
+          <t>Grönberget, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607260.2241394727</v>
+        <v>607384</v>
       </c>
       <c r="R3" t="n">
-        <v>7218028.923913302</v>
+        <v>7217970</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,53 +858,67 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79774888</v>
+        <v>79774894</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608007.8345767669</v>
+        <v>607288</v>
       </c>
       <c r="R4" t="n">
-        <v>7218110.926191169</v>
+        <v>7218043</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +961,9 @@
           <t>2019-09-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,53 +990,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79774880</v>
+        <v>94318482</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grönberget, Ly lm</t>
+          <t>Grönberget, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608254.619767428</v>
+        <v>607673</v>
       </c>
       <c r="R5" t="n">
-        <v>7218301.097862757</v>
+        <v>7218277</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,31 +1071,45 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79774897</v>
+        <v>94318485</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1117,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grönberget, Ly lm</t>
+          <t>Grönberget, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607625.8269881769</v>
+        <v>607975</v>
       </c>
       <c r="R6" t="n">
-        <v>7218010.473559937</v>
+        <v>7218237</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,31 +1187,45 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79774881</v>
+        <v>94318495</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,17 +1253,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grönberget, Ly lm</t>
+          <t>Grönberget, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608247.9094690447</v>
+        <v>608161</v>
       </c>
       <c r="R7" t="n">
-        <v>7218299.586246504</v>
+        <v>7218528</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1287,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,31 +1303,45 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79774891</v>
+        <v>94318518</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,37 +1349,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grönberget, Ly lm</t>
+          <t>Grönberget, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608233.9671316349</v>
+        <v>607248</v>
       </c>
       <c r="R8" t="n">
-        <v>7218287.675048905</v>
+        <v>7218031</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1403,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,69 +1419,83 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79774889</v>
+        <v>98887979</v>
       </c>
       <c r="B9" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>3009</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Antrodia piceata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>K.Runnel, V.Spirin &amp; J.Vlasák</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grönberget, Ly lm</t>
+          <t>Grönberget, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607219.8201427819</v>
+        <v>607949</v>
       </c>
       <c r="R9" t="n">
-        <v>7217976.781433504</v>
+        <v>7218222</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1519,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,33 +1533,58 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79774900</v>
+        <v>94318511</v>
       </c>
       <c r="B10" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,37 +1592,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grönberget, Ly lm</t>
+          <t>Grönberget, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607639.264692604</v>
+        <v>607397</v>
       </c>
       <c r="R10" t="n">
-        <v>7218013.072395901</v>
+        <v>7217982</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,22 +1646,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,31 +1662,45 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79774890</v>
+        <v>79774900</v>
       </c>
       <c r="B11" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,38 +1708,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607898.8423678013</v>
+        <v>607639</v>
       </c>
       <c r="R11" t="n">
-        <v>7217910.140103519</v>
+        <v>7218013</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,19 +1765,9 @@
           <t>2019-09-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,15 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79774862</v>
+        <v>79774892</v>
       </c>
       <c r="B12" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607572.9029217234</v>
+        <v>608100</v>
       </c>
       <c r="R12" t="n">
-        <v>7218070.643178934</v>
+        <v>7217915</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1872,19 +1862,9 @@
           <t>2019-09-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,15 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>79774893</v>
+        <v>94318484</v>
       </c>
       <c r="B13" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,37 +1902,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grönberget, Ly lm</t>
+          <t>Grönberget, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>608260.6392748015</v>
+        <v>607718</v>
       </c>
       <c r="R13" t="n">
-        <v>7218298.360987983</v>
+        <v>7218254</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,22 +1956,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,31 +1972,45 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79774894</v>
+        <v>94318507</v>
       </c>
       <c r="B14" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,37 +2018,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grönberget, Ly lm</t>
+          <t>Grönberget, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607287.639713451</v>
+        <v>607834</v>
       </c>
       <c r="R14" t="n">
-        <v>7218042.584953149</v>
+        <v>7217939</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,22 +2072,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,31 +2088,45 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94318495</v>
+        <v>79774888</v>
       </c>
       <c r="B15" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,37 +2134,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grönberget, Storuman, Ly lm</t>
+          <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>608160.9468732409</v>
+        <v>608008</v>
       </c>
       <c r="R15" t="n">
-        <v>7218527.846172576</v>
+        <v>7218111</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,22 +2188,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,50 +2204,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94318481</v>
+        <v>79774889</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,37 +2231,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grönberget, Storuman, Ly lm</t>
+          <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607673.2658302758</v>
+        <v>607220</v>
       </c>
       <c r="R16" t="n">
-        <v>7218276.582628942</v>
+        <v>7217977</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,22 +2285,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,50 +2301,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94318488</v>
+        <v>94318515</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,21 +2328,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2437,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607971.4807747768</v>
+        <v>607252</v>
       </c>
       <c r="R17" t="n">
-        <v>7218494.345595486</v>
+        <v>7218032</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,21 +2385,11 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2496,17 +2401,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2528,53 +2433,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94318480</v>
+        <v>79774862</v>
       </c>
       <c r="B18" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grönberget, Storuman, Ly lm</t>
+          <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607673.2658302758</v>
+        <v>607573</v>
       </c>
       <c r="R18" t="n">
-        <v>7218276.582628942</v>
+        <v>7218071</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,22 +2498,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,50 +2514,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94318518</v>
+        <v>79774864</v>
       </c>
       <c r="B19" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,37 +2541,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grönberget, Storuman, Ly lm</t>
+          <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607247.4633221428</v>
+        <v>607260</v>
       </c>
       <c r="R19" t="n">
-        <v>7218030.997214743</v>
+        <v>7218029</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,22 +2595,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,50 +2611,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94318510</v>
+        <v>94318508</v>
       </c>
       <c r="B20" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,10 +2662,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607492.5170437589</v>
+        <v>607832</v>
       </c>
       <c r="R20" t="n">
-        <v>7218025.0741925</v>
+        <v>7217948</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,19 +2695,9 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2921,15 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>94318509</v>
+        <v>94318510</v>
       </c>
       <c r="B21" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,21 +2754,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2961,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607492.4407069996</v>
+        <v>607493</v>
       </c>
       <c r="R21" t="n">
-        <v>7218027.183240277</v>
+        <v>7218025</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2994,19 +2811,9 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3052,15 +2859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>94318507</v>
+        <v>94318481</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3068,21 +2870,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3092,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607833.5298877172</v>
+        <v>607673</v>
       </c>
       <c r="R22" t="n">
-        <v>7217938.601806032</v>
+        <v>7218277</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3125,21 +2927,11 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3151,17 +2943,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3183,37 +2975,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>94318491</v>
+        <v>94318517</v>
       </c>
       <c r="B23" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3223,10 +3010,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607923.5171980361</v>
+        <v>607246</v>
       </c>
       <c r="R23" t="n">
-        <v>7218557.635537874</v>
+        <v>7218032</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,21 +3043,11 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3279,6 +3056,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3299,53 +3091,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>94318508</v>
+        <v>79774877</v>
       </c>
       <c r="B24" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grönberget, Storuman, Ly lm</t>
+          <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607832.363605909</v>
+        <v>607315</v>
       </c>
       <c r="R24" t="n">
-        <v>7217947.429393955</v>
+        <v>7218046</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3369,22 +3156,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3395,72 +3172,48 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>94318517</v>
+        <v>94318480</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3470,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607246.5729973821</v>
+        <v>607673</v>
       </c>
       <c r="R25" t="n">
-        <v>7218032.232138801</v>
+        <v>7218277</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3503,19 +3256,9 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3561,53 +3304,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>94318482</v>
+        <v>79774890</v>
       </c>
       <c r="B26" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grönberget, Storuman, Ly lm</t>
+          <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607673.2658302758</v>
+        <v>607899</v>
       </c>
       <c r="R26" t="n">
-        <v>7218276.582628942</v>
+        <v>7217910</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3631,22 +3373,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3657,50 +3389,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>94318494</v>
+        <v>79774885</v>
       </c>
       <c r="B27" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3708,37 +3416,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grönberget, Storuman, Ly lm</t>
+          <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>608153.7687234972</v>
+        <v>608034</v>
       </c>
       <c r="R27" t="n">
-        <v>7218527.584699783</v>
+        <v>7218094</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3762,22 +3474,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3788,72 +3490,48 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>94318485</v>
+        <v>94318513</v>
       </c>
       <c r="B28" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>208260</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3863,10 +3541,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607974.5170598387</v>
+        <v>607283</v>
       </c>
       <c r="R28" t="n">
-        <v>7218236.418692827</v>
+        <v>7218019</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3896,21 +3574,11 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3919,21 +3587,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3954,37 +3607,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>94318484</v>
+        <v>94318491</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3994,10 +3642,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607718.4772258056</v>
+        <v>607923</v>
       </c>
       <c r="R29" t="n">
-        <v>7218254.149460834</v>
+        <v>7218557</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4027,21 +3675,11 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4050,21 +3688,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4085,15 +3708,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>94318514</v>
+        <v>94318509</v>
       </c>
       <c r="B30" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4125,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607254.3726768525</v>
+        <v>607492</v>
       </c>
       <c r="R30" t="n">
-        <v>7218027.023146487</v>
+        <v>7218027</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4158,19 +3776,9 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4216,37 +3824,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>94318513</v>
+        <v>94318514</v>
       </c>
       <c r="B31" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208260</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4256,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607282.5501673887</v>
+        <v>607255</v>
       </c>
       <c r="R31" t="n">
-        <v>7218019.593701359</v>
+        <v>7218027</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4289,21 +3892,11 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4312,6 +3905,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4332,15 +3940,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>94318515</v>
+        <v>94318516</v>
       </c>
       <c r="B32" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4348,21 +3951,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4372,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607252.5006202513</v>
+        <v>607251</v>
       </c>
       <c r="R32" t="n">
-        <v>7218032.02384565</v>
+        <v>7218033</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4405,19 +4008,9 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4463,53 +4056,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>94318516</v>
+        <v>79774893</v>
       </c>
       <c r="B33" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>760</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grönberget, Storuman, Ly lm</t>
+          <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607251.6102936213</v>
+        <v>608261</v>
       </c>
       <c r="R33" t="n">
-        <v>7218033.258767854</v>
+        <v>7218298</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4533,22 +4121,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4559,88 +4137,64 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>98887979</v>
+        <v>79774891</v>
       </c>
       <c r="B34" t="n">
-        <v>89668</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3009</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Resinoporia piceata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Runnel, Spirin &amp; Vlasák) Audet</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grönberget, Storuman, Ly lm</t>
+          <t>Grönberget, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>607948.8260020723</v>
+        <v>608234</v>
       </c>
       <c r="R34" t="n">
-        <v>7218221.969830873</v>
+        <v>7218288</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4664,22 +4218,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4688,51 +4232,409 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>79774874</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Grönberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>608289</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7218301</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>79774881</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Grönberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>608248</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7218300</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>79774876</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grönberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>608289</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7218301</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>79774880</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Grönberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>608255</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7218301</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
